--- a/Tuan5/TestCase_Bai5.xlsx
+++ b/Tuan5/TestCase_Bai5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\HCMUNRE\Tester\Tuan5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C48FA7-7263-4E80-BFE9-7CE2C7E8CF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F959FB-E35F-4E37-9413-CEA77D800FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E897814A-3AC5-464E-8CED-9ABEF34E6823}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{E897814A-3AC5-464E-8CED-9ABEF34E6823}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -881,7 +881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -922,8 +922,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1451,17 +1450,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEC45DC0-1792-4651-9AEE-4ADAB22EC17B}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.21875" customWidth="1"/>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
-    <col min="3" max="3" width="27.88671875" customWidth="1"/>
-    <col min="4" max="4" width="30.21875" customWidth="1"/>
-    <col min="5" max="5" width="31.109375" customWidth="1"/>
-    <col min="6" max="6" width="26.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1475,7 +1474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1492,13 +1491,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1518,8 +1517,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
@@ -1533,7 +1532,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>1</v>
       </c>
@@ -1547,7 +1546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>2</v>
       </c>
@@ -1561,7 +1560,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>3</v>
       </c>
@@ -1575,7 +1574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>4</v>
       </c>
@@ -1589,7 +1588,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E13" s="12">
         <v>5</v>
       </c>
@@ -1597,7 +1596,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E14" s="12">
         <v>6</v>
       </c>
@@ -1605,7 +1604,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E15" s="12">
         <v>7</v>
       </c>
@@ -1613,10 +1612,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E16" s="12">
         <v>8</v>
       </c>
@@ -1624,10 +1620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E17" s="12">
         <v>9</v>
       </c>
@@ -1635,10 +1628,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="16"/>
       <c r="E18" s="14">
         <v>10</v>
       </c>
@@ -1646,32 +1637,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="17"/>
-    </row>
-    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="17" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="230.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>15</v>
       </c>
@@ -1691,7 +1680,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="214.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="214.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>16</v>
       </c>
@@ -1707,11 +1696,11 @@
       <c r="E22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="19" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="240.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="18" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="240.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>17</v>
       </c>
@@ -1727,11 +1716,11 @@
       <c r="E23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="19" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="18" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="262.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>18</v>
       </c>
@@ -1747,11 +1736,11 @@
       <c r="E24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="19" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="255.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F24" s="18" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="255.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>19</v>
       </c>
@@ -1767,11 +1756,11 @@
       <c r="E25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="19" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="255.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="18" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="255.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>50</v>
       </c>
@@ -1787,11 +1776,11 @@
       <c r="E26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="19" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="264.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F26" s="18" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="264.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>52</v>
       </c>
@@ -1807,11 +1796,11 @@
       <c r="E27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="19" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="198.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="18" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="198.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>54</v>
       </c>
@@ -1827,11 +1816,11 @@
       <c r="E28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="19" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="249" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F28" s="18" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="249" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>56</v>
       </c>
@@ -1851,7 +1840,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="222.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="222.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>58</v>
       </c>
@@ -1867,11 +1856,11 @@
       <c r="E30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="19" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="253.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F30" s="18" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="253.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>61</v>
       </c>
@@ -1887,11 +1876,11 @@
       <c r="E31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="19" t="e" vm="11">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="253.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="18" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="253.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>62</v>
       </c>
@@ -1907,11 +1896,11 @@
       <c r="E32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="19" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="262.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F32" s="18" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="262.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>64</v>
       </c>
@@ -1927,11 +1916,11 @@
       <c r="E33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="19" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="253.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F33" s="18" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="253.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>67</v>
       </c>
@@ -1947,11 +1936,11 @@
       <c r="E34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="19" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="249.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F34" s="18" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="249.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>70</v>
       </c>
@@ -1967,11 +1956,11 @@
       <c r="E35" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="19" t="e" vm="15">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="268.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F35" s="18" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="268.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>73</v>
       </c>
@@ -1987,11 +1976,11 @@
       <c r="E36" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="19" t="e" vm="16">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="18" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="244.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>76</v>
       </c>
@@ -2007,11 +1996,11 @@
       <c r="E37" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F37" s="19" t="e" vm="17">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="256.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F37" s="18" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="256.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>78</v>
       </c>
@@ -2027,11 +2016,11 @@
       <c r="E38" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="19" t="e" vm="18">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="213.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F38" s="18" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="213.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>80</v>
       </c>
@@ -2047,11 +2036,11 @@
       <c r="E39" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="19" t="e" vm="19">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="205.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F39" s="18" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="205.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>82</v>
       </c>
@@ -2067,11 +2056,11 @@
       <c r="E40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="19" t="e" vm="20">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="225.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F40" s="18" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="225.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>84</v>
       </c>
@@ -2087,11 +2076,11 @@
       <c r="E41" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="19" t="e" vm="21">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="234.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F41" s="18" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="234.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>86</v>
       </c>
@@ -2107,11 +2096,11 @@
       <c r="E42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="19" t="e" vm="22">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="245.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F42" s="18" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="245.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>88</v>
       </c>
@@ -2127,11 +2116,11 @@
       <c r="E43" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F43" s="19" t="e" vm="23">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F43" s="18" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>90</v>
       </c>
@@ -2147,9 +2136,9 @@
       <c r="E44" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="19"/>
-    </row>
-    <row r="45" spans="1:6" ht="284.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F44" s="18"/>
+    </row>
+    <row r="45" spans="1:6" ht="284.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>93</v>
       </c>
@@ -2165,11 +2154,11 @@
       <c r="E45" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F45" s="19" t="e" vm="24">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F45" s="18" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>96</v>
       </c>
@@ -2185,9 +2174,9 @@
       <c r="E46" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="19"/>
-    </row>
-    <row r="47" spans="1:6" ht="258.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F46" s="18"/>
+    </row>
+    <row r="47" spans="1:6" ht="258.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>99</v>
       </c>
@@ -2203,11 +2192,11 @@
       <c r="E47" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="19" t="e" vm="25">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F47" s="18" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>101</v>
       </c>
@@ -2223,9 +2212,9 @@
       <c r="E48" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="19"/>
-    </row>
-    <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F48" s="18"/>
+    </row>
+    <row r="49" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>103</v>
       </c>
@@ -2241,25 +2230,25 @@
       <c r="E49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F49" s="19"/>
-    </row>
-    <row r="50" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F49" s="18"/>
+    </row>
+    <row r="50" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>108</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="21"/>
+      <c r="F50" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
